--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.36861231648132</v>
+        <v>6.559899501428214</v>
       </c>
       <c r="D2" t="n">
-        <v>40.12948190331552</v>
+        <v>6.521040809288771</v>
       </c>
       <c r="E2" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F2" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.36995159056045</v>
+        <v>3.960117133466073</v>
       </c>
       <c r="D3" t="n">
-        <v>24.10038704436084</v>
+        <v>3.916312894708636</v>
       </c>
       <c r="E3" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F3" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.37685153329754</v>
+        <v>2.66123837416085</v>
       </c>
       <c r="D4" t="n">
-        <v>16.16212999729792</v>
+        <v>2.626346124560912</v>
       </c>
       <c r="E4" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F4" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.17708928638439</v>
+        <v>6.366277009037463</v>
       </c>
       <c r="D5" t="n">
-        <v>39.27474790057463</v>
+        <v>6.382146533843378</v>
       </c>
       <c r="E5" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F5" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.15256051937429</v>
+        <v>4.574791084398322</v>
       </c>
       <c r="D6" t="n">
-        <v>28.25843279709383</v>
+        <v>4.591995329527747</v>
       </c>
       <c r="E6" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F6" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.93548778812123</v>
+        <v>4.8645167655697</v>
       </c>
       <c r="D7" t="n">
-        <v>29.72546940199641</v>
+        <v>4.830388777824417</v>
       </c>
       <c r="E7" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F7" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.31754772267936</v>
+        <v>6.389101504935396</v>
       </c>
       <c r="D8" t="n">
-        <v>39.21011773880507</v>
+        <v>6.371644132555825</v>
       </c>
       <c r="E8" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F8" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.53973720728523</v>
+        <v>4.800207296183849</v>
       </c>
       <c r="D9" t="n">
-        <v>29.78960888270469</v>
+        <v>4.840811443439512</v>
       </c>
       <c r="E9" t="n">
-        <v>7.849459797826522</v>
+        <v>1.27553721714681</v>
       </c>
       <c r="F9" t="n">
-        <v>7.884874372656419</v>
+        <v>1.281292085556668</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
